--- a/artfynd/A 17684-2026 artfynd.xlsx
+++ b/artfynd/A 17684-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>108644444</v>
+        <v>127702270</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lövås, Vg</t>
+          <t>Risveden /Skigeri flug, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>339785.6366489184</v>
+        <v>339738</v>
       </c>
       <c r="R2" t="n">
-        <v>6434210.200187849</v>
+        <v>6434210</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,27 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-04-29</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-04-29</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>cirka 10 m2. Intill liten bäck och litet alkärr.</t>
+          <t>3 kuddar varav den största med omkrets 40-50 xm</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,34 +769,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Gerre</t>
+          <t>Linus Lundin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>108644607</v>
+        <v>127702946</v>
       </c>
       <c r="B3" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,16 +798,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -839,28 +816,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lövås, Vg</t>
+          <t>Risveden /Skigeri flug, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>339730.092939486</v>
+        <v>339738</v>
       </c>
       <c r="R3" t="n">
-        <v>6434229.401543891</v>
+        <v>6434210</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-04-29</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-04-29</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,22 +881,573 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>108644672</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lövås, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>339671</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6434246</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-04-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-04-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>I senvuxen död gran vid kanten av sumpskog</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Lars Gerre</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Lars Gerre</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>108644607</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lövås, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>339730</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6434230</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-04-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-04-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127702181</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Risveden /Skigeri flug, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>339738</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6434210</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-20</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ett 20 tal plantor inom 20kvm område på hällrygg</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>108644444</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lövås, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>339785</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6434210</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>cirka 10 m2. Intill liten bäck och litet alkärr.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118637775</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Risveden /Skigeri flug, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>339738</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6434210</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hålanda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-23</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>6-7 fläckar av havstulpanlav på dels död stam och levande stam av ek i barrblandskog i sluttning nära sumpskog.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linus Lundin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17684-2026 artfynd.xlsx
+++ b/artfynd/A 17684-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702270</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702946</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108644672</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1115,6 +1135,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108644607</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1223,6 +1248,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127702181</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108644444</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,8 +1483,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118637775</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>